--- a/andmed.xlsx
+++ b/andmed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arturilumae\Desktop\Programeerimine2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7816696-F181-4167-A913-F4DC63166A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEFBF9A-5AEC-4FEC-8753-B7B7ACF94EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
   </bookViews>
@@ -36,15 +36,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Alampiir</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>Kodutöö+praktikum</t>
   </si>
   <si>
-    <t>projekt</t>
+    <t>alampiir</t>
+  </si>
+  <si>
+    <t>testid</t>
+  </si>
+  <si>
+    <t>Projekt</t>
+  </si>
+  <si>
+    <t>1.kontrolltöö</t>
+  </si>
+  <si>
+    <t>2.kontrolltöö</t>
+  </si>
+  <si>
+    <t>Eksam</t>
+  </si>
+  <si>
+    <t>Lisaülesanded</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HinndeSkaala: </t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Max punkt</t>
   </si>
 </sst>
 </file>
@@ -417,29 +465,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354938B-0846-47E9-A425-CCAF3D8DCC63}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="19.26953125" customWidth="1"/>
     <col min="2" max="2" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>7</v>
       </c>
-      <c r="C2">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>5</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <f>SUM(C2:C8)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/andmed.xlsx
+++ b/andmed.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arturilumae\Desktop\Programeerimine2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hannelahaavel\.vscode\Programeerimine2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEFBF9A-5AEC-4FEC-8753-B7B7ACF94EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBD42C3-C8B8-477F-BACF-3270864149E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
   </bookViews>
   <sheets>
     <sheet name="Programeerimine" sheetId="1" r:id="rId1"/>
+    <sheet name="Arvuti arhitektuur ja riistvara" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -133,7 +134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normaallaad" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -149,7 +150,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office'i kujundus">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -466,13 +467,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354938B-0846-47E9-A425-CCAF3D8DCC63}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" customWidth="1"/>
-    <col min="2" max="2" width="17.6328125" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -480,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -491,7 +492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -502,7 +503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -513,7 +514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -524,7 +525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -535,7 +536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -546,7 +547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -554,7 +555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -563,7 +564,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -577,7 +578,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -588,7 +589,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>14</v>
       </c>
@@ -599,7 +600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -610,7 +611,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -621,7 +622,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -635,4 +636,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E182D063-A4A4-41E9-8F3C-1F5407B14D19}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/andmed.xlsx
+++ b/andmed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hannelahaavel\.vscode\Programeerimine2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBD42C3-C8B8-477F-BACF-3270864149E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC816921-E124-497A-AF85-BB3DBA7CBD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="1" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
   </bookViews>
   <sheets>
     <sheet name="Programeerimine" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Kodutöö+praktikum</t>
   </si>
@@ -94,6 +94,18 @@
   </si>
   <si>
     <t>Max punkt</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>kontrolltööd</t>
+  </si>
+  <si>
+    <t>eksam</t>
+  </si>
+  <si>
+    <t>kohvripraktikum</t>
   </si>
 </sst>
 </file>
@@ -640,9 +652,88 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E182D063-A4A4-41E9-8F3C-1F5407B14D19}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>51</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>68</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/andmed.xlsx
+++ b/andmed.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arturilumae\Desktop\Programeerimine2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEFBF9A-5AEC-4FEC-8753-B7B7ACF94EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A221C8FD-895D-4459-A149-91F1066E670A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
   </bookViews>
   <sheets>
-    <sheet name="Programeerimine" sheetId="1" r:id="rId1"/>
+    <sheet name="Programeerimine 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -465,22 +465,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354938B-0846-47E9-A425-CCAF3D8DCC63}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
     <col min="2" max="2" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -490,8 +502,17 @@
       <c r="C2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -501,8 +522,17 @@
       <c r="C3">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -512,8 +542,17 @@
       <c r="C4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -523,8 +562,17 @@
       <c r="C5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -534,8 +582,17 @@
       <c r="C6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -546,7 +603,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -554,82 +611,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="C9">
         <f>SUM(C2:C8)</f>
         <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/andmed.xlsx
+++ b/andmed.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hannelahaavel\.vscode\Programeerimine2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arturilumae\Desktop\Programeerimine2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6E3D2C-982F-4346-A7F5-6F6DF0609E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC899E5-D628-4AE4-AAA2-2233F3D6362A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="4" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{976ED3E9-5FED-40E8-A46D-11A0466F8880}"/>
   </bookViews>
   <sheets>
-    <sheet name="Programeerimine" sheetId="1" r:id="rId1"/>
-    <sheet name="Aar" sheetId="2" r:id="rId2"/>
-    <sheet name="KÕM I" sheetId="3" r:id="rId3"/>
+    <sheet name="Programmeerimine 1" sheetId="1" r:id="rId1"/>
+    <sheet name="AAR 1" sheetId="2" r:id="rId2"/>
+    <sheet name="KÕM 1" sheetId="3" r:id="rId3"/>
     <sheet name="Opsys" sheetId="4" r:id="rId4"/>
     <sheet name="Sissejuhatus erialasse" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="52">
   <si>
     <t>Kodutöö+praktikum</t>
   </si>
@@ -96,9 +96,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>Max punkt</t>
-  </si>
-  <si>
     <t>max</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>vaja saada, et eksamit teha</t>
   </si>
   <si>
-    <t>kokku</t>
-  </si>
-  <si>
     <t>hindamisskaala:</t>
   </si>
   <si>
@@ -199,6 +193,9 @@
   </si>
   <si>
     <t>kõigi 7 peale peab kokku saama 15</t>
+  </si>
+  <si>
+    <t>UUS</t>
   </si>
 </sst>
 </file>
@@ -239,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normaallaad" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -255,7 +252,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office'i kujundus">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -571,22 +568,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354938B-0846-47E9-A425-CCAF3D8DCC63}">
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -596,8 +596,17 @@
       <c r="C2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -607,8 +616,17 @@
       <c r="C3">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -618,8 +636,17 @@
       <c r="C4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -629,8 +656,17 @@
       <c r="C5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -640,8 +676,17 @@
       <c r="C6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -651,91 +696,22 @@
       <c r="C7">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
         <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9">
-        <f>SUM(C2:C8)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -745,34 +721,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E182D063-A4A4-41E9-8F3C-1F5407B14D19}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.90625" customWidth="1"/>
+    <col min="5" max="5" width="14.1796875" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>20</v>
       </c>
       <c r="B2">
         <v>51</v>
@@ -780,28 +750,19 @@
       <c r="C2">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>20</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>21</v>
       </c>
       <c r="B3">
         <v>51</v>
@@ -809,28 +770,19 @@
       <c r="C3">
         <v>100</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>21</v>
-      </c>
-      <c r="F3">
-        <v>68</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="I3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -838,56 +790,79 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="G4">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>68</v>
+      </c>
+      <c r="C7">
         <v>100</v>
       </c>
-      <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7">
-        <v>51</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -898,30 +873,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A63D56A-7CF6-4758-B300-60A50F090A1F}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>20</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -939,9 +914,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -959,9 +934,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -979,9 +954,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -999,9 +974,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>20</v>
@@ -1022,16 +997,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>215</v>
-      </c>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F7" t="s">
         <v>17</v>
       </c>
@@ -1049,27 +1015,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81F3794-B083-422F-923D-4B4E103D8825}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.6328125" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -1077,19 +1043,19 @@
       <c r="C2">
         <v>60</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -1097,66 +1063,57 @@
       <c r="C3">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6">
         <v>50</v>
       </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E7" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>50</v>
       </c>
     </row>
@@ -1167,28 +1124,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29392844-CCEA-4616-8B61-7F32D2510E75}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.36328125" customWidth="1"/>
+    <col min="4" max="4" width="30.453125" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1206,9 +1163,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1226,9 +1183,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1246,9 +1203,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1266,9 +1223,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1277,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -1289,9 +1246,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1309,9 +1266,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1320,9 +1277,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1331,12 +1288,12 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1345,9 +1302,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1356,12 +1313,12 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1370,9 +1327,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1381,9 +1338,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1392,9 +1349,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1403,9 +1360,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1414,9 +1371,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1425,9 +1382,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1436,18 +1393,7 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19">
         <v>50</v>
-      </c>
-      <c r="C19">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
